--- a/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 3,12</t>
+          <t>-5,68; 3,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1,6</t>
+          <t>-8,0; 1,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,88</t>
+          <t>-0,77; 3,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,19</t>
+          <t>-5,32; 1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,2</t>
+          <t>0,58; 6,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,54</t>
+          <t>-100,0; 124,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,81</t>
+          <t>-1,67; 2,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,01</t>
+          <t>1,79; 9,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,25</t>
+          <t>-2,01; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,82</t>
+          <t>-5,2; 1,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,6</t>
+          <t>0,82; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,22</t>
+          <t>-1,73; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,13</t>
+          <t>-1,22; 1,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,9</t>
+          <t>-0,74; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,59</t>
+          <t>-0,91; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 309,13</t>
+          <t>-79,37; 404,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 396,35</t>
+          <t>-37,13; 299,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 297,13</t>
+          <t>-38,44; 320,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 3,15</t>
+          <t>-5,23; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,45</t>
+          <t>-8,19; 1,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,44</t>
+          <t>-0,69; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,17</t>
+          <t>-5,87; 1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,66</t>
+          <t>0,51; 7,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,45</t>
+          <t>-100,0; 141,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,84</t>
+          <t>-1,67; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,99</t>
+          <t>1,5; 9,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,74</t>
+          <t>-2,0; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 1,1</t>
+          <t>-5,44; 1,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,42</t>
+          <t>0,8; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,02</t>
+          <t>-1,56; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,27</t>
+          <t>-1,18; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,74</t>
+          <t>-0,79; 2,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,7</t>
+          <t>-0,93; 2,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 404,08</t>
+          <t>-81,02; 379,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 299,11</t>
+          <t>-39,77; 258,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 320,9</t>
+          <t>-41,91; 242,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,04</t>
+          <t>-5,93; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,63</t>
+          <t>-8,79; 1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,47</t>
+          <t>-0,7; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,17</t>
+          <t>-5,76; 1,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,03</t>
+          <t>0,49; 6,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,87</t>
+          <t>-100,0; 131,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,75</t>
+          <t>-1,66; 2,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,45</t>
+          <t>1,76; 11,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,47</t>
+          <t>-2,02; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,19</t>
+          <t>-5,24; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,1</t>
+          <t>0,8; 7,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,76</t>
+          <t>-1,8; 5,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,22</t>
+          <t>-1,24; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,75</t>
+          <t>-0,74; 2,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,58</t>
+          <t>-0,79; 2,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 379,39</t>
+          <t>-81,22; 309,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 258,1</t>
+          <t>-35,86; 396,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 242,58</t>
+          <t>-38,01; 297,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-31,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-57,81%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9227531619486723</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.516900895565724</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-0.3134298202744367</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.5781371763431543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 3,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,79; 1,6</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-5.925000002249336</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-8.78831422675022</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>3.122340505112086</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.596867824592405</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>178,6%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-51,01%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>519,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; 3,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 1,19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 6,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 131,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.096028348731983</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.779856854751447</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.952693639549625</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.785967397994056</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5100649362970917</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>5.19968525593861</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.7032890987522376</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.761509846641729</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4854755162382101</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 2,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 11,01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 4,25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.879131368217246</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.186850922998865</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.195125805126758</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.315354905405582</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +741,223 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-62,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.08885140902127608</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.567735477361216</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8464196179063158</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.1077522698028903</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.8571463093273737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,24; 1,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 7,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,8; 5,22</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.65951689070029</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.763225487195404</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.02069078363489</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.806510650228022</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.01386258742327</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.251515502444883</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.539116579362027</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.650196955432921</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.041464913806282</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6286570399228496</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7527051820084073</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.240252762874179</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8045927293496978</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.799347578727047</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.822069482556786</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.595919839857364</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.217247859274542</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,16%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 1,13</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 2,9</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 2,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-81,22; 309,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-35,86; 396,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-38,01; 297,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.01129055055764383</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9243879343079033</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8388304965545604</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.01156439558567262</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.5441273032485812</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.5017371236590873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.236873151634271</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7366684071880731</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.7905734161701663</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.8122246853555277</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3585518719476887</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3800751984856841</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.125210289242748</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.904313393394856</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.589864854486734</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>3.091292136617253</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.963457609350142</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.971283089795334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +966,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
